--- a/data/trans_orig/IP29B_2023-Habitat-trans_orig.xlsx
+++ b/data/trans_orig/IP29B_2023-Habitat-trans_orig.xlsx
@@ -489,7 +489,7 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Meses con lactancia materna exclusiva</t>
+          <t>Meses con lactancia materna exclusiva (tasa de respuesta: 97,51%)</t>
         </is>
       </c>
       <c r="B1" s="2" t="n"/>
@@ -571,17 +571,17 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
-          <t>6,8; 9,83</t>
+          <t>6,69; 9,68</t>
         </is>
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>6,69; 10,1</t>
+          <t>6,73; 9,97</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>7,07; 9,39</t>
+          <t>7,19; 9,31</t>
         </is>
       </c>
     </row>
@@ -621,17 +621,17 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
-          <t>7,86; 11,17</t>
+          <t>7,84; 10,99</t>
         </is>
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>7,38; 10,29</t>
+          <t>7,4; 10,14</t>
         </is>
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>7,89; 9,94</t>
+          <t>7,87; 9,92</t>
         </is>
       </c>
     </row>
@@ -671,17 +671,17 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>7,3; 10,87</t>
+          <t>7,43; 11,42</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>7,63; 11,33</t>
+          <t>7,79; 11,33</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>8,04; 10,57</t>
+          <t>8,05; 10,59</t>
         </is>
       </c>
     </row>
@@ -721,17 +721,17 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
-          <t>7,32; 10,06</t>
+          <t>7,19; 9,94</t>
         </is>
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>7,67; 10,11</t>
+          <t>7,57; 9,96</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>7,75; 9,6</t>
+          <t>7,79; 9,64</t>
         </is>
       </c>
     </row>
@@ -771,17 +771,17 @@
       </c>
       <c r="C13" s="2" t="inlineStr">
         <is>
-          <t>7,98; 9,63</t>
+          <t>8,0; 9,6</t>
         </is>
       </c>
       <c r="D13" s="2" t="inlineStr">
         <is>
-          <t>7,89; 9,47</t>
+          <t>7,99; 9,5</t>
         </is>
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>8,19; 9,31</t>
+          <t>8,22; 9,32</t>
         </is>
       </c>
     </row>

--- a/data/trans_orig/IP29B_2023-Habitat-trans_orig.xlsx
+++ b/data/trans_orig/IP29B_2023-Habitat-trans_orig.xlsx
@@ -571,17 +571,17 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
-          <t>6,69; 9,68</t>
+          <t>6,86; 9,89</t>
         </is>
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>6,73; 9,97</t>
+          <t>6,65; 10,23</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>7,19; 9,31</t>
+          <t>7,11; 9,43</t>
         </is>
       </c>
     </row>
@@ -621,17 +621,17 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
-          <t>7,84; 10,99</t>
+          <t>7,88; 11,0</t>
         </is>
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>7,4; 10,14</t>
+          <t>7,36; 10,11</t>
         </is>
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>7,87; 9,92</t>
+          <t>7,94; 9,96</t>
         </is>
       </c>
     </row>
@@ -671,17 +671,17 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>7,43; 11,42</t>
+          <t>7,43; 11,14</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>7,79; 11,33</t>
+          <t>7,68; 11,38</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>8,05; 10,59</t>
+          <t>8,08; 10,54</t>
         </is>
       </c>
     </row>
@@ -721,17 +721,17 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
-          <t>7,19; 9,94</t>
+          <t>7,06; 9,96</t>
         </is>
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>7,57; 9,96</t>
+          <t>7,6; 10,1</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>7,79; 9,64</t>
+          <t>7,77; 9,66</t>
         </is>
       </c>
     </row>
@@ -771,17 +771,17 @@
       </c>
       <c r="C13" s="2" t="inlineStr">
         <is>
-          <t>8,0; 9,6</t>
+          <t>7,99; 9,6</t>
         </is>
       </c>
       <c r="D13" s="2" t="inlineStr">
         <is>
-          <t>7,99; 9,5</t>
+          <t>8,02; 9,57</t>
         </is>
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>8,22; 9,32</t>
+          <t>8,17; 9,32</t>
         </is>
       </c>
     </row>
